--- a/Excel_Practice_Files/Day3_All Practice More.xlsx
+++ b/Excel_Practice_Files/Day3_All Practice More.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cadd Mentor\Student_Class_Code\Jazaul_Hasan_Data_Anylytics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cadd Mentor\Student_Class_Code\Jazaul_Hasan_Data_Anylytics\Excel_Practice_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21F67FF-93AD-430D-8921-903CFFA55137}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABECF5F4-0F25-4795-9B3A-6A2BB3F4C13B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Practice Date Formule" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,10 @@
     <sheet name="Sheet2" sheetId="11" r:id="rId5"/>
     <sheet name="Scenario Summary 2" sheetId="20" r:id="rId6"/>
     <sheet name="Scenario PivotTable" sheetId="21" r:id="rId7"/>
-    <sheet name="Sheet10" sheetId="17" r:id="rId8"/>
-    <sheet name="Sheet5" sheetId="7" r:id="rId9"/>
-    <sheet name="Sheet6" sheetId="8" r:id="rId10"/>
+    <sheet name="Scenario Summary 3" sheetId="22" r:id="rId8"/>
+    <sheet name="Sheet10" sheetId="17" r:id="rId9"/>
+    <sheet name="Sheet5" sheetId="7" r:id="rId10"/>
+    <sheet name="Sheet6" sheetId="8" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="budget">#REF!</definedName>
@@ -43,8 +44,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId11"/>
-    <pivotCache cacheId="1" r:id="rId12"/>
+    <pivotCache cacheId="0" r:id="rId12"/>
+    <pivotCache cacheId="1" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="80">
   <si>
     <t>Today</t>
   </si>
@@ -305,7 +306,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,6 +373,30 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="18"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -593,7 +618,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -671,6 +696,21 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2045,11 +2085,11 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <f ca="1">TODAY()</f>
-        <v>46051</v>
+        <v>46115</v>
       </c>
       <c r="B2" s="5">
         <f ca="1">NOW()</f>
-        <v>46051.468694328702</v>
+        <v>46115.406346875003</v>
       </c>
       <c r="C2">
         <f ca="1">YEAR(B2)</f>
@@ -2057,33 +2097,33 @@
       </c>
       <c r="D2">
         <f ca="1">MONTH(B2)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <f ca="1">DAY(B2)</f>
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <f ca="1">HOUR(B2)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <f ca="1">MINUTE(B2)</f>
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H2">
         <f ca="1">SECOND(B2)</f>
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="I2" s="5">
         <f ca="1">EDATE(A2,4)</f>
-        <v>46171</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I4" s="4">
         <f ca="1">EDATE(A2,3*12)</f>
-        <v>47147</v>
+        <v>47211</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2103,6 +2143,723 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C6DFC98-DCB1-4F4A-B660-D875D1C50D6F}">
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="21">
+        <v>43106</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="7">
+        <v>95</v>
+      </c>
+      <c r="G2" s="7">
+        <v>1198</v>
+      </c>
+      <c r="H2" s="7">
+        <v>113810</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="21">
+        <v>43157</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="7">
+        <v>27</v>
+      </c>
+      <c r="G3" s="7">
+        <v>225</v>
+      </c>
+      <c r="H3" s="7">
+        <v>6075</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="21">
+        <v>43344</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="7">
+        <v>2</v>
+      </c>
+      <c r="G4" s="7">
+        <v>125</v>
+      </c>
+      <c r="H4" s="7">
+        <v>250</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="21">
+        <v>43123</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="7">
+        <v>50</v>
+      </c>
+      <c r="G5" s="7">
+        <v>500</v>
+      </c>
+      <c r="H5" s="7">
+        <v>25000</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="21">
+        <v>43429</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="7">
+        <v>96</v>
+      </c>
+      <c r="G6" s="7">
+        <v>58.5</v>
+      </c>
+      <c r="H6" s="7">
+        <v>5616</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="21">
+        <v>43140</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="7">
+        <v>36</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1198</v>
+      </c>
+      <c r="H7" s="7">
+        <v>43128</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="22">
+        <v>43174</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="9">
+        <v>56</v>
+      </c>
+      <c r="G8" s="9">
+        <v>1198</v>
+      </c>
+      <c r="H8" s="9">
+        <v>67088</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="21">
+        <v>43208</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="7">
+        <v>75</v>
+      </c>
+      <c r="G9" s="7">
+        <v>1198</v>
+      </c>
+      <c r="H9" s="7">
+        <v>89850</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="21">
+        <v>43225</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="7">
+        <v>90</v>
+      </c>
+      <c r="G10" s="7">
+        <v>1198</v>
+      </c>
+      <c r="H10" s="7">
+        <v>107820</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="22">
+        <v>43701</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="9">
+        <v>3</v>
+      </c>
+      <c r="G11" s="9">
+        <v>125</v>
+      </c>
+      <c r="H11" s="9">
+        <v>375</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="22">
+        <v>43378</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="9">
+        <v>28</v>
+      </c>
+      <c r="G12" s="9">
+        <v>500</v>
+      </c>
+      <c r="H12" s="9">
+        <v>14000</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="21">
+        <v>43616</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="7">
+        <v>80</v>
+      </c>
+      <c r="G13" s="7">
+        <v>500</v>
+      </c>
+      <c r="H13" s="7">
+        <v>40000</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="22">
+        <v>43803</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="9">
+        <v>94</v>
+      </c>
+      <c r="G14" s="9">
+        <v>500</v>
+      </c>
+      <c r="H14" s="9">
+        <v>47000</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="21">
+        <v>43242</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="7">
+        <v>32</v>
+      </c>
+      <c r="G15" s="7">
+        <v>1198</v>
+      </c>
+      <c r="H15" s="7">
+        <v>38336</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="22">
+        <v>43276</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="9">
+        <v>90</v>
+      </c>
+      <c r="G16" s="9">
+        <v>1198</v>
+      </c>
+      <c r="H16" s="9">
+        <v>107820</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="21">
+        <v>43327</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="7">
+        <v>35</v>
+      </c>
+      <c r="G17" s="7">
+        <v>1198</v>
+      </c>
+      <c r="H17" s="7">
+        <v>41930</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="21">
+        <v>43395</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="7">
+        <v>64</v>
+      </c>
+      <c r="G18" s="7">
+        <v>225</v>
+      </c>
+      <c r="H18" s="7">
+        <v>14400</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="22">
+        <v>43412</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="9">
+        <v>15</v>
+      </c>
+      <c r="G19" s="9">
+        <v>225</v>
+      </c>
+      <c r="H19" s="9">
+        <v>3375</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="21">
+        <v>43191</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="7">
+        <v>60</v>
+      </c>
+      <c r="G20" s="7">
+        <v>500</v>
+      </c>
+      <c r="H20" s="7">
+        <v>30000</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="22">
+        <v>43514</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="9">
+        <v>4</v>
+      </c>
+      <c r="G21" s="9">
+        <v>500</v>
+      </c>
+      <c r="H21" s="9">
+        <v>2000</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="21">
+        <v>43293</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="7">
+        <v>29</v>
+      </c>
+      <c r="G22" s="7">
+        <v>500</v>
+      </c>
+      <c r="H22" s="7">
+        <v>14500</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="22">
+        <v>43310</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="9">
+        <v>81</v>
+      </c>
+      <c r="G23" s="9">
+        <v>500</v>
+      </c>
+      <c r="H23" s="9">
+        <v>40500</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>43259</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="2">
+        <v>60</v>
+      </c>
+      <c r="G24" s="2">
+        <v>500</v>
+      </c>
+      <c r="H24" s="2">
+        <v>30000</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62693AF5-4D24-4E87-A163-2F584BD005EC}">
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3766,7 +4523,7 @@
         <v>500</v>
       </c>
       <c r="F5">
-        <f t="dataTable" ref="F5:F18" dt2D="0" dtr="0" r1="C4"/>
+        <f t="dataTable" ref="F5:F18" dt2D="0" dtr="0" r1="C4" ca="1"/>
         <v>27500</v>
       </c>
     </row>
@@ -3840,7 +4597,7 @@
         <v>500</v>
       </c>
       <c r="J8">
-        <f t="dataTable" ref="J8:Q19" dt2D="1" dtr="1" r1="C6" r2="C4" ca="1"/>
+        <f t="dataTable" ref="J8:Q19" dt2D="1" dtr="1" r1="C6" r2="C4"/>
         <v>27500</v>
       </c>
       <c r="K8">
@@ -4277,7 +5034,7 @@
         <v>500</v>
       </c>
       <c r="F6">
-        <f t="dataTable" ref="F6:F16" dt2D="0" dtr="0" r1="D5" ca="1"/>
+        <f t="dataTable" ref="F6:F16" dt2D="0" dtr="0" r1="D5"/>
         <v>50000</v>
       </c>
       <c r="I6">
@@ -4320,7 +5077,7 @@
         <v>500</v>
       </c>
       <c r="J7">
-        <f t="dataTable" ref="J7:O20" dt2D="1" dtr="1" r1="D7" r2="D5"/>
+        <f t="dataTable" ref="J7:O20" dt2D="1" dtr="1" r1="D7" r2="D5" ca="1"/>
         <v>50000</v>
       </c>
       <c r="K7">
@@ -5051,6 +5808,172 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCA5D7E-3CEC-45DD-BDA3-3B3B6020C346}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="B1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="17.33203125" bestFit="1" customWidth="1" outlineLevel="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+    </row>
+    <row r="3" spans="2:7" ht="15.6" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="20.399999999999999" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+    </row>
+    <row r="6" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="56"/>
+      <c r="C6" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="42">
+        <v>300</v>
+      </c>
+      <c r="E6" s="52">
+        <v>300</v>
+      </c>
+      <c r="F6" s="52">
+        <v>700</v>
+      </c>
+      <c r="G6" s="52">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="56"/>
+      <c r="C7" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="42">
+        <v>400</v>
+      </c>
+      <c r="E7" s="52">
+        <v>400</v>
+      </c>
+      <c r="F7" s="52">
+        <v>600</v>
+      </c>
+      <c r="G7" s="52">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="56"/>
+      <c r="C8" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="42">
+        <v>500</v>
+      </c>
+      <c r="E8" s="52">
+        <v>500</v>
+      </c>
+      <c r="F8" s="52">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="52">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+    </row>
+    <row r="10" spans="2:7" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="58"/>
+      <c r="C10" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="43">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="43">
+        <v>1200</v>
+      </c>
+      <c r="F10" s="43">
+        <v>2300</v>
+      </c>
+      <c r="G10" s="43">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D68A8824-82C0-49F6-9FED-35C62F8EBEE6}">
   <dimension ref="A3:F14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5153,721 +6076,4 @@
   </scenarios>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C6DFC98-DCB1-4F4A-B660-D875D1C50D6F}">
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.5546875" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="21">
-        <v>43106</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="7">
-        <v>95</v>
-      </c>
-      <c r="G2" s="7">
-        <v>1198</v>
-      </c>
-      <c r="H2" s="7">
-        <v>113810</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="21">
-        <v>43157</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="7">
-        <v>27</v>
-      </c>
-      <c r="G3" s="7">
-        <v>225</v>
-      </c>
-      <c r="H3" s="7">
-        <v>6075</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="21">
-        <v>43344</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="7">
-        <v>2</v>
-      </c>
-      <c r="G4" s="7">
-        <v>125</v>
-      </c>
-      <c r="H4" s="7">
-        <v>250</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="21">
-        <v>43123</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="7">
-        <v>50</v>
-      </c>
-      <c r="G5" s="7">
-        <v>500</v>
-      </c>
-      <c r="H5" s="7">
-        <v>25000</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
-        <v>43429</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="7">
-        <v>96</v>
-      </c>
-      <c r="G6" s="7">
-        <v>58.5</v>
-      </c>
-      <c r="H6" s="7">
-        <v>5616</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
-        <v>43140</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="7">
-        <v>36</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1198</v>
-      </c>
-      <c r="H7" s="7">
-        <v>43128</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="22">
-        <v>43174</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="9">
-        <v>56</v>
-      </c>
-      <c r="G8" s="9">
-        <v>1198</v>
-      </c>
-      <c r="H8" s="9">
-        <v>67088</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="21">
-        <v>43208</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="7">
-        <v>75</v>
-      </c>
-      <c r="G9" s="7">
-        <v>1198</v>
-      </c>
-      <c r="H9" s="7">
-        <v>89850</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
-        <v>43225</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="7">
-        <v>90</v>
-      </c>
-      <c r="G10" s="7">
-        <v>1198</v>
-      </c>
-      <c r="H10" s="7">
-        <v>107820</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="22">
-        <v>43701</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="9">
-        <v>3</v>
-      </c>
-      <c r="G11" s="9">
-        <v>125</v>
-      </c>
-      <c r="H11" s="9">
-        <v>375</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="22">
-        <v>43378</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="9">
-        <v>28</v>
-      </c>
-      <c r="G12" s="9">
-        <v>500</v>
-      </c>
-      <c r="H12" s="9">
-        <v>14000</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="21">
-        <v>43616</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="7">
-        <v>80</v>
-      </c>
-      <c r="G13" s="7">
-        <v>500</v>
-      </c>
-      <c r="H13" s="7">
-        <v>40000</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="22">
-        <v>43803</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="9">
-        <v>94</v>
-      </c>
-      <c r="G14" s="9">
-        <v>500</v>
-      </c>
-      <c r="H14" s="9">
-        <v>47000</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="21">
-        <v>43242</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="7">
-        <v>32</v>
-      </c>
-      <c r="G15" s="7">
-        <v>1198</v>
-      </c>
-      <c r="H15" s="7">
-        <v>38336</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="22">
-        <v>43276</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="9">
-        <v>90</v>
-      </c>
-      <c r="G16" s="9">
-        <v>1198</v>
-      </c>
-      <c r="H16" s="9">
-        <v>107820</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="21">
-        <v>43327</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="7">
-        <v>35</v>
-      </c>
-      <c r="G17" s="7">
-        <v>1198</v>
-      </c>
-      <c r="H17" s="7">
-        <v>41930</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
-        <v>43395</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="7">
-        <v>64</v>
-      </c>
-      <c r="G18" s="7">
-        <v>225</v>
-      </c>
-      <c r="H18" s="7">
-        <v>14400</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="22">
-        <v>43412</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="9">
-        <v>15</v>
-      </c>
-      <c r="G19" s="9">
-        <v>225</v>
-      </c>
-      <c r="H19" s="9">
-        <v>3375</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="21">
-        <v>43191</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="7">
-        <v>60</v>
-      </c>
-      <c r="G20" s="7">
-        <v>500</v>
-      </c>
-      <c r="H20" s="7">
-        <v>30000</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="22">
-        <v>43514</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="9">
-        <v>4</v>
-      </c>
-      <c r="G21" s="9">
-        <v>500</v>
-      </c>
-      <c r="H21" s="9">
-        <v>2000</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="21">
-        <v>43293</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="7">
-        <v>29</v>
-      </c>
-      <c r="G22" s="7">
-        <v>500</v>
-      </c>
-      <c r="H22" s="7">
-        <v>14500</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="22">
-        <v>43310</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="9">
-        <v>81</v>
-      </c>
-      <c r="G23" s="9">
-        <v>500</v>
-      </c>
-      <c r="H23" s="9">
-        <v>40500</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="11">
-        <v>43259</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="2">
-        <v>60</v>
-      </c>
-      <c r="G24" s="2">
-        <v>500</v>
-      </c>
-      <c r="H24" s="2">
-        <v>30000</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>